--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122979784</v>
+        <v>122982584</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471465</v>
+        <v>471572</v>
       </c>
       <c r="R4" t="n">
-        <v>7026527</v>
+        <v>7026541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122982580</v>
+        <v>122983059</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,7 +1026,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471453</v>
+        <v>471480</v>
       </c>
       <c r="R5" t="n">
-        <v>7026499</v>
+        <v>7026453</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982584</v>
+        <v>122982234</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R6" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122982234</v>
+        <v>122979397</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471541</v>
+        <v>471433</v>
       </c>
       <c r="R7" t="n">
-        <v>7026540</v>
+        <v>7026636</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,6 +1307,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1325,6 +1320,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1341,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122979598</v>
+        <v>122980835</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,51 +1377,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471408</v>
+        <v>471462</v>
       </c>
       <c r="R8" t="n">
-        <v>7026599</v>
+        <v>7026487</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,6 +1447,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1444,7 +1463,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1482,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122983059</v>
+        <v>123010707</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,42 +1522,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471480</v>
+        <v>471506</v>
       </c>
       <c r="R9" t="n">
-        <v>7026453</v>
+        <v>7026544</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,14 +1579,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,51 +1602,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122980835</v>
+        <v>123010706</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,39 +1634,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471462</v>
+        <v>471547</v>
       </c>
       <c r="R10" t="n">
-        <v>7026487</v>
+        <v>7026555</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,14 +1691,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,22 +1718,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122979397</v>
+        <v>122979829</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,37 +1746,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471433</v>
+        <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026636</v>
+        <v>7026527</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,7 +1822,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,27 +1836,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1860,6 +1876,1090 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123010711</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471445</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7026715</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123010708</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471490</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7026516</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123010703</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>471553</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7026553</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123010705</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>471553</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7026553</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122982580</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>471453</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7026499</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123010710</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>471465</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7026544</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123010709</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>471477</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7026477</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123010700</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Aspås V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>471596</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7026584</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122979598</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>471408</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7026599</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982654</v>
+        <v>122982584</v>
       </c>
       <c r="B2" t="n">
-        <v>57428</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471555</v>
+        <v>471572</v>
       </c>
       <c r="R2" t="n">
-        <v>7026552</v>
+        <v>7026541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982584</v>
+        <v>122982234</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R4" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1127,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982234</v>
+        <v>122982654</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1130,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471541</v>
+        <v>471555</v>
       </c>
       <c r="R6" t="n">
-        <v>7026540</v>
+        <v>7026552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122980835</v>
+        <v>123010709</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,42 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471462</v>
+        <v>471477</v>
       </c>
       <c r="R8" t="n">
-        <v>7026487</v>
+        <v>7026477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,14 +1434,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,53 +1457,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010707</v>
+        <v>123010706</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1546,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471506</v>
+        <v>471547</v>
       </c>
       <c r="R9" t="n">
-        <v>7026544</v>
+        <v>7026555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010706</v>
+        <v>122982580</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,37 +1601,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471547</v>
+        <v>471453</v>
       </c>
       <c r="R10" t="n">
-        <v>7026555</v>
+        <v>7026499</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,19 +1670,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:01</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,23 +1688,53 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122979829</v>
+        <v>122980835</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1771,21 +1775,17 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471465</v>
+        <v>471462</v>
       </c>
       <c r="R11" t="n">
-        <v>7026527</v>
+        <v>7026487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010711</v>
+        <v>122979829</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,34 +1895,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471445</v>
+        <v>471465</v>
       </c>
       <c r="R12" t="n">
-        <v>7026715</v>
+        <v>7026527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,19 +1964,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:31</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,26 +1982,56 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010708</v>
+        <v>123010703</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,34 +2044,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471490</v>
+        <v>471553</v>
       </c>
       <c r="R13" t="n">
-        <v>7026516</v>
+        <v>7026553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2108,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,7 +2118,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2150,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010703</v>
+        <v>123010707</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,39 +2166,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471553</v>
+        <v>471506</v>
       </c>
       <c r="R14" t="n">
-        <v>7026553</v>
+        <v>7026544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2225,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,12 +2235,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010705</v>
+        <v>123010711</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,21 +2278,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2265,10 +2302,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471553</v>
+        <v>471445</v>
       </c>
       <c r="R15" t="n">
-        <v>7026553</v>
+        <v>7026715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2337,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2347,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,10 +2374,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122982580</v>
+        <v>123010700</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,49 +2390,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471453</v>
+        <v>471596</v>
       </c>
       <c r="R16" t="n">
-        <v>7026499</v>
+        <v>7026584</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2422,14 +2447,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,56 +2470,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010710</v>
+        <v>122979598</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2502,37 +2502,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471465</v>
+        <v>471408</v>
       </c>
       <c r="R17" t="n">
-        <v>7026544</v>
+        <v>7026599</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2559,21 +2573,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2582,26 +2586,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010709</v>
+        <v>123010708</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,21 +2643,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2638,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471477</v>
+        <v>471490</v>
       </c>
       <c r="R18" t="n">
-        <v>7026477</v>
+        <v>7026516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2673,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2683,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010700</v>
+        <v>123010705</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2726,21 +2755,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2750,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471596</v>
+        <v>471553</v>
       </c>
       <c r="R19" t="n">
-        <v>7026584</v>
+        <v>7026553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2785,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2795,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2822,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122979598</v>
+        <v>123010710</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2838,51 +2867,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471408</v>
+        <v>471465</v>
       </c>
       <c r="R20" t="n">
-        <v>7026599</v>
+        <v>7026544</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2909,11 +2924,21 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2922,41 +2947,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982584</v>
+        <v>122982234</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R2" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982459</v>
+        <v>122983059</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471541</v>
+        <v>471480</v>
       </c>
       <c r="R3" t="n">
-        <v>7026540</v>
+        <v>7026453</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,6 +860,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982234</v>
+        <v>122982584</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471541</v>
+        <v>471572</v>
       </c>
       <c r="R4" t="n">
-        <v>7026540</v>
+        <v>7026541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122983059</v>
+        <v>122982459</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471480</v>
+        <v>471541</v>
       </c>
       <c r="R5" t="n">
-        <v>7026453</v>
+        <v>7026540</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,11 +1094,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,31 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982654</v>
+        <v>122979397</v>
       </c>
       <c r="B6" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,50 +1130,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471555</v>
+        <v>471433</v>
       </c>
       <c r="R6" t="n">
-        <v>7026552</v>
+        <v>7026636</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,6 +1196,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1213,6 +1209,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122979397</v>
+        <v>122982654</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,41 +1262,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471433</v>
+        <v>471555</v>
       </c>
       <c r="R7" t="n">
-        <v>7026636</v>
+        <v>7026552</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,11 +1337,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1320,31 +1345,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010709</v>
+        <v>122979784</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1377,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471477</v>
+        <v>471465</v>
       </c>
       <c r="R8" t="n">
-        <v>7026477</v>
+        <v>7026527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,19 +1446,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs minst 5 meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,23 +1464,53 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010706</v>
+        <v>123010710</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1513,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471547</v>
+        <v>471465</v>
       </c>
       <c r="R9" t="n">
-        <v>7026555</v>
+        <v>7026544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122982580</v>
+        <v>123010711</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,49 +1638,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471453</v>
+        <v>471445</v>
       </c>
       <c r="R10" t="n">
-        <v>7026499</v>
+        <v>7026715</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,14 +1695,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,56 +1718,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122980835</v>
+        <v>123010706</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,42 +1750,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471462</v>
+        <v>471547</v>
       </c>
       <c r="R11" t="n">
-        <v>7026487</v>
+        <v>7026555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,14 +1807,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,56 +1830,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122979829</v>
+        <v>123010708</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,46 +1862,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471465</v>
+        <v>471490</v>
       </c>
       <c r="R12" t="n">
-        <v>7026527</v>
+        <v>7026516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,14 +1919,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,56 +1942,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010703</v>
+        <v>123010705</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,29 +1974,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
@@ -2108,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2118,12 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2262,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010711</v>
+        <v>123010709</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2278,21 +2198,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2302,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471445</v>
+        <v>471477</v>
       </c>
       <c r="R15" t="n">
-        <v>7026715</v>
+        <v>7026477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2347,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2409,7 @@
         <v>122979598</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2627,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010708</v>
+        <v>122982580</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,37 +2563,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471490</v>
+        <v>471453</v>
       </c>
       <c r="R18" t="n">
-        <v>7026516</v>
+        <v>7026499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2700,19 +2632,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:52</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,26 +2650,56 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010705</v>
+        <v>122980835</v>
       </c>
       <c r="B19" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,34 +2712,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471553</v>
+        <v>471462</v>
       </c>
       <c r="R19" t="n">
-        <v>7026553</v>
+        <v>7026487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2812,19 +2777,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:01</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,26 +2795,56 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010710</v>
+        <v>123010703</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,34 +2857,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471465</v>
+        <v>471553</v>
       </c>
       <c r="R20" t="n">
-        <v>7026544</v>
+        <v>7026553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2921,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2931,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982234</v>
+        <v>122982459</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122983059</v>
+        <v>122982234</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471480</v>
+        <v>471541</v>
       </c>
       <c r="R3" t="n">
-        <v>7026453</v>
+        <v>7026540</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +855,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982584</v>
+        <v>122982654</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>57428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471572</v>
+        <v>471555</v>
       </c>
       <c r="R4" t="n">
-        <v>7026541</v>
+        <v>7026552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122982459</v>
+        <v>122979397</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471541</v>
+        <v>471433</v>
       </c>
       <c r="R5" t="n">
-        <v>7026540</v>
+        <v>7026636</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,6 +1068,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,6 +1081,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122979397</v>
+        <v>122983059</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,34 +1138,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471433</v>
+        <v>471480</v>
       </c>
       <c r="R6" t="n">
-        <v>7026636</v>
+        <v>7026453</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,27 +1221,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1250,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122982654</v>
+        <v>122982584</v>
       </c>
       <c r="B7" t="n">
-        <v>57428</v>
+        <v>90948</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,47 +1271,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471555</v>
+        <v>471572</v>
       </c>
       <c r="R7" t="n">
-        <v>7026552</v>
+        <v>7026541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122979784</v>
+        <v>123010703</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1395,28 +1395,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471465</v>
+        <v>471553</v>
       </c>
       <c r="R8" t="n">
-        <v>7026527</v>
+        <v>7026553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,14 +1439,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs minst 5 meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,53 +1467,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010710</v>
+        <v>123010708</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1550,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471465</v>
+        <v>471490</v>
       </c>
       <c r="R9" t="n">
-        <v>7026544</v>
+        <v>7026516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010711</v>
+        <v>122982580</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,37 +1611,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471445</v>
+        <v>471453</v>
       </c>
       <c r="R10" t="n">
-        <v>7026715</v>
+        <v>7026499</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,19 +1680,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:31</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,16 +1698,46 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1846,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010708</v>
+        <v>123010709</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,21 +1872,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471490</v>
+        <v>471477</v>
       </c>
       <c r="R12" t="n">
-        <v>7026516</v>
+        <v>7026477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1941,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010705</v>
+        <v>122979829</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,34 +1984,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471553</v>
+        <v>471465</v>
       </c>
       <c r="R13" t="n">
-        <v>7026553</v>
+        <v>7026527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,19 +2053,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:01</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,26 +2071,56 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010707</v>
+        <v>122979598</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,37 +2133,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471506</v>
+        <v>471408</v>
       </c>
       <c r="R14" t="n">
-        <v>7026544</v>
+        <v>7026599</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2143,21 +2204,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2166,26 +2217,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010709</v>
+        <v>122980835</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,34 +2274,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471477</v>
+        <v>471462</v>
       </c>
       <c r="R15" t="n">
-        <v>7026477</v>
+        <v>7026487</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,19 +2339,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,26 +2357,56 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010700</v>
+        <v>123010705</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,21 +2419,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2443,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471596</v>
+        <v>471553</v>
       </c>
       <c r="R16" t="n">
-        <v>7026584</v>
+        <v>7026553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2478,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2488,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122979598</v>
+        <v>123010700</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,51 +2531,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471408</v>
+        <v>471596</v>
       </c>
       <c r="R17" t="n">
-        <v>7026599</v>
+        <v>7026584</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,11 +2588,21 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2506,51 +2611,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122982580</v>
+        <v>123010711</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,49 +2643,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471453</v>
+        <v>471445</v>
       </c>
       <c r="R18" t="n">
-        <v>7026499</v>
+        <v>7026715</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2632,14 +2700,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,56 +2723,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122980835</v>
+        <v>123010707</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,42 +2755,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471462</v>
+        <v>471506</v>
       </c>
       <c r="R19" t="n">
-        <v>7026487</v>
+        <v>7026544</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,14 +2812,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,56 +2835,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010703</v>
+        <v>123010710</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2857,39 +2867,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471553</v>
+        <v>471465</v>
       </c>
       <c r="R20" t="n">
-        <v>7026553</v>
+        <v>7026544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2931,12 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982459</v>
+        <v>122982584</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471541</v>
+        <v>471572</v>
       </c>
       <c r="R2" t="n">
-        <v>7026540</v>
+        <v>7026541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982234</v>
+        <v>122982654</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471541</v>
+        <v>471555</v>
       </c>
       <c r="R3" t="n">
-        <v>7026540</v>
+        <v>7026552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982654</v>
+        <v>122982234</v>
       </c>
       <c r="B4" t="n">
-        <v>57428</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471555</v>
+        <v>471541</v>
       </c>
       <c r="R4" t="n">
-        <v>7026552</v>
+        <v>7026540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979397</v>
+        <v>122982459</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471433</v>
+        <v>471541</v>
       </c>
       <c r="R5" t="n">
-        <v>7026636</v>
+        <v>7026540</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,11 +1068,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1081,31 +1076,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1259,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122982584</v>
+        <v>122979397</v>
       </c>
       <c r="B7" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471572</v>
+        <v>471433</v>
       </c>
       <c r="R7" t="n">
-        <v>7026541</v>
+        <v>7026636</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,6 +1307,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1345,6 +1320,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010703</v>
+        <v>122979598</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,42 +1377,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471553</v>
+        <v>471408</v>
       </c>
       <c r="R8" t="n">
-        <v>7026553</v>
+        <v>7026599</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,26 +1448,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1467,26 +1461,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010708</v>
+        <v>122979829</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,34 +1518,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471490</v>
+        <v>471465</v>
       </c>
       <c r="R9" t="n">
-        <v>7026516</v>
+        <v>7026527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,19 +1587,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:52</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,23 +1605,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122982580</v>
+        <v>122980835</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1633,27 +1689,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471453</v>
+        <v>471462</v>
       </c>
       <c r="R10" t="n">
-        <v>7026499</v>
+        <v>7026487</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,7 +1739,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,12 +1773,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1856,10 +1908,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010709</v>
+        <v>123010705</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,21 +1924,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1896,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471477</v>
+        <v>471553</v>
       </c>
       <c r="R12" t="n">
-        <v>7026477</v>
+        <v>7026553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122979829</v>
+        <v>123010708</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,46 +2036,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471465</v>
+        <v>471490</v>
       </c>
       <c r="R13" t="n">
-        <v>7026527</v>
+        <v>7026516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,14 +2093,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,56 +2116,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122979598</v>
+        <v>123010707</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2133,51 +2148,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471408</v>
+        <v>471506</v>
       </c>
       <c r="R14" t="n">
-        <v>7026599</v>
+        <v>7026544</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,11 +2205,21 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2217,51 +2228,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122980835</v>
+        <v>123010709</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2274,42 +2260,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471462</v>
+        <v>471477</v>
       </c>
       <c r="R15" t="n">
-        <v>7026487</v>
+        <v>7026477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,14 +2317,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,56 +2340,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010705</v>
+        <v>123010700</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2419,21 +2372,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2443,10 +2396,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471553</v>
+        <v>471596</v>
       </c>
       <c r="R16" t="n">
-        <v>7026553</v>
+        <v>7026584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2478,7 +2431,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2488,7 +2441,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010700</v>
+        <v>122982580</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,37 +2484,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471596</v>
+        <v>471453</v>
       </c>
       <c r="R17" t="n">
-        <v>7026584</v>
+        <v>7026499</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2588,19 +2553,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:09</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:09</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,23 +2571,53 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010711</v>
+        <v>123010710</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2667,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471445</v>
+        <v>471465</v>
       </c>
       <c r="R18" t="n">
-        <v>7026715</v>
+        <v>7026544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2702,7 +2692,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2702,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,10 +2729,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010707</v>
+        <v>123010703</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,34 +2745,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471506</v>
+        <v>471553</v>
       </c>
       <c r="R19" t="n">
-        <v>7026544</v>
+        <v>7026553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,7 +2809,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2824,7 +2819,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,7 +2851,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010710</v>
+        <v>123010711</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471465</v>
+        <v>471445</v>
       </c>
       <c r="R20" t="n">
-        <v>7026544</v>
+        <v>7026715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982584</v>
+        <v>122982459</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R2" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982234</v>
+        <v>122979397</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471541</v>
+        <v>471433</v>
       </c>
       <c r="R4" t="n">
-        <v>7026540</v>
+        <v>7026636</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,6 +966,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,6 +979,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -990,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122982459</v>
+        <v>122983059</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,37 +1036,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471541</v>
+        <v>471480</v>
       </c>
       <c r="R5" t="n">
-        <v>7026540</v>
+        <v>7026453</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,6 +1103,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,6 +1116,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1092,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122983059</v>
+        <v>122982584</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,42 +1173,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471480</v>
+        <v>471572</v>
       </c>
       <c r="R6" t="n">
-        <v>7026453</v>
+        <v>7026541</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,11 +1235,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1188,31 +1243,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122979397</v>
+        <v>122982234</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471433</v>
+        <v>471541</v>
       </c>
       <c r="R7" t="n">
-        <v>7026636</v>
+        <v>7026540</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,11 +1337,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1320,31 +1345,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122979598</v>
+        <v>122979829</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,36 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1415,13 +1413,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471408</v>
+        <v>471465</v>
       </c>
       <c r="R8" t="n">
-        <v>7026599</v>
+        <v>7026527</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,6 +1451,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1464,7 +1467,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1479,12 +1487,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1502,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122979829</v>
+        <v>123010700</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,46 +1526,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471465</v>
+        <v>471596</v>
       </c>
       <c r="R9" t="n">
-        <v>7026527</v>
+        <v>7026584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,14 +1583,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,56 +1606,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122980835</v>
+        <v>123010711</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,42 +1638,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471462</v>
+        <v>471445</v>
       </c>
       <c r="R10" t="n">
-        <v>7026487</v>
+        <v>7026715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1732,14 +1695,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,53 +1718,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010706</v>
+        <v>123010710</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1836,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471547</v>
+        <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026555</v>
+        <v>7026544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1871,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1881,7 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010705</v>
+        <v>123010709</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1924,21 +1862,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1948,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471553</v>
+        <v>471477</v>
       </c>
       <c r="R12" t="n">
-        <v>7026553</v>
+        <v>7026477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1983,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010708</v>
+        <v>122979598</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,37 +1974,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471490</v>
+        <v>471408</v>
       </c>
       <c r="R13" t="n">
-        <v>7026516</v>
+        <v>7026599</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2093,21 +2045,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2116,26 +2058,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010707</v>
+        <v>123010705</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,21 +2115,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471506</v>
+        <v>471553</v>
       </c>
       <c r="R14" t="n">
-        <v>7026544</v>
+        <v>7026553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010709</v>
+        <v>122982580</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,37 +2227,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471477</v>
+        <v>471453</v>
       </c>
       <c r="R15" t="n">
-        <v>7026477</v>
+        <v>7026499</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2317,19 +2296,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,23 +2314,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010700</v>
+        <v>123010707</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2396,10 +2400,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471596</v>
+        <v>471506</v>
       </c>
       <c r="R16" t="n">
-        <v>7026584</v>
+        <v>7026544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2468,7 +2472,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122982580</v>
+        <v>123010703</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2502,31 +2506,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471453</v>
+        <v>471553</v>
       </c>
       <c r="R17" t="n">
-        <v>7026499</v>
+        <v>7026553</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2553,14 +2550,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,56 +2578,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010710</v>
+        <v>122980835</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2633,34 +2610,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471465</v>
+        <v>471462</v>
       </c>
       <c r="R18" t="n">
-        <v>7026544</v>
+        <v>7026487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,19 +2675,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,26 +2693,56 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010703</v>
+        <v>123010708</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,39 +2755,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471553</v>
+        <v>471490</v>
       </c>
       <c r="R19" t="n">
-        <v>7026553</v>
+        <v>7026516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2819,12 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,7 +2851,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010711</v>
+        <v>123010706</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471445</v>
+        <v>471547</v>
       </c>
       <c r="R20" t="n">
-        <v>7026715</v>
+        <v>7026555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122982459</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982654</v>
+        <v>122982584</v>
       </c>
       <c r="B3" t="n">
-        <v>57428</v>
+        <v>90951</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471555</v>
+        <v>471572</v>
       </c>
       <c r="R3" t="n">
-        <v>7026552</v>
+        <v>7026541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122979397</v>
+        <v>122982234</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471433</v>
+        <v>471541</v>
       </c>
       <c r="R4" t="n">
-        <v>7026636</v>
+        <v>7026540</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,11 +957,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,31 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1020,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122983059</v>
+        <v>122979397</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471480</v>
+        <v>471433</v>
       </c>
       <c r="R5" t="n">
-        <v>7026453</v>
+        <v>7026636</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1105,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,27 +1075,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982584</v>
+        <v>122982654</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,38 +1125,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471572</v>
+        <v>471555</v>
       </c>
       <c r="R6" t="n">
-        <v>7026541</v>
+        <v>7026552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122982234</v>
+        <v>122983059</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,37 +1240,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471541</v>
+        <v>471480</v>
       </c>
       <c r="R7" t="n">
-        <v>7026540</v>
+        <v>7026453</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,6 +1307,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1345,6 +1320,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122979829</v>
+        <v>123010710</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,46 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>471465</v>
       </c>
       <c r="R8" t="n">
-        <v>7026527</v>
+        <v>7026544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,14 +1434,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,56 +1457,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010700</v>
+        <v>123010705</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1550,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471596</v>
+        <v>471553</v>
       </c>
       <c r="R9" t="n">
-        <v>7026584</v>
+        <v>7026553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010711</v>
+        <v>122980835</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,34 +1601,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471445</v>
+        <v>471462</v>
       </c>
       <c r="R10" t="n">
-        <v>7026715</v>
+        <v>7026487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,19 +1666,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:31</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,26 +1684,56 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010710</v>
+        <v>122979829</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,34 +1746,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026544</v>
+        <v>7026527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,19 +1815,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,26 +1833,56 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010709</v>
+        <v>123010711</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,21 +1895,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471477</v>
+        <v>471445</v>
       </c>
       <c r="R12" t="n">
-        <v>7026477</v>
+        <v>7026715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122979598</v>
+        <v>123010708</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,51 +2007,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471408</v>
+        <v>471490</v>
       </c>
       <c r="R13" t="n">
-        <v>7026599</v>
+        <v>7026516</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2045,11 +2064,21 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2058,51 +2087,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010705</v>
+        <v>123010703</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,24 +2119,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
@@ -2174,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2193,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122982580</v>
+        <v>122979598</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,34 +2241,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2263,13 +2279,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471453</v>
+        <v>471408</v>
       </c>
       <c r="R15" t="n">
-        <v>7026499</v>
+        <v>7026599</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2301,11 +2317,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2317,12 +2328,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2337,12 +2343,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2360,10 +2366,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010707</v>
+        <v>123010709</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90951</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,21 +2382,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2400,10 +2406,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471506</v>
+        <v>471477</v>
       </c>
       <c r="R16" t="n">
-        <v>7026544</v>
+        <v>7026477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2435,7 +2441,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2445,7 +2451,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2478,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010703</v>
+        <v>123010700</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2488,39 +2494,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471553</v>
+        <v>471596</v>
       </c>
       <c r="R17" t="n">
-        <v>7026553</v>
+        <v>7026584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2552,7 +2553,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2562,12 +2563,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122980835</v>
+        <v>123010706</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,42 +2606,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471462</v>
+        <v>471547</v>
       </c>
       <c r="R18" t="n">
-        <v>7026487</v>
+        <v>7026555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2675,14 +2663,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,56 +2686,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010708</v>
+        <v>122982580</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,37 +2718,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471490</v>
+        <v>471453</v>
       </c>
       <c r="R19" t="n">
-        <v>7026516</v>
+        <v>7026499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2812,19 +2787,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:52</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,26 +2805,56 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010706</v>
+        <v>123010707</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471547</v>
+        <v>471506</v>
       </c>
       <c r="R20" t="n">
-        <v>7026555</v>
+        <v>7026544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982459</v>
+        <v>122982234</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>122982584</v>
       </c>
       <c r="B3" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982234</v>
+        <v>122983059</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471541</v>
+        <v>471480</v>
       </c>
       <c r="R4" t="n">
-        <v>7026540</v>
+        <v>7026453</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,6 +962,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979397</v>
+        <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>57431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +1028,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471433</v>
+        <v>471555</v>
       </c>
       <c r="R5" t="n">
-        <v>7026636</v>
+        <v>7026552</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,11 +1103,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1072,31 +1111,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982654</v>
+        <v>122982459</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,47 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471555</v>
+        <v>471541</v>
       </c>
       <c r="R6" t="n">
-        <v>7026552</v>
+        <v>7026540</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122983059</v>
+        <v>122979397</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,39 +1245,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471480</v>
+        <v>471433</v>
       </c>
       <c r="R7" t="n">
-        <v>7026453</v>
+        <v>7026636</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010710</v>
+        <v>123010706</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471465</v>
+        <v>471547</v>
       </c>
       <c r="R8" t="n">
-        <v>7026544</v>
+        <v>7026555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010705</v>
+        <v>122979829</v>
       </c>
       <c r="B9" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1489,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471553</v>
+        <v>471465</v>
       </c>
       <c r="R9" t="n">
-        <v>7026553</v>
+        <v>7026527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,19 +1558,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:01</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,26 +1576,56 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122980835</v>
+        <v>123010708</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,42 +1638,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471462</v>
+        <v>471490</v>
       </c>
       <c r="R10" t="n">
-        <v>7026487</v>
+        <v>7026516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,14 +1695,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,56 +1718,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122979829</v>
+        <v>123010710</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,46 +1750,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026527</v>
+        <v>7026544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,14 +1807,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,56 +1830,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010711</v>
+        <v>122982580</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,37 +1862,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471445</v>
+        <v>471453</v>
       </c>
       <c r="R12" t="n">
-        <v>7026715</v>
+        <v>7026499</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,19 +1931,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:31</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,26 +1949,56 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010708</v>
+        <v>123010700</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471490</v>
+        <v>471596</v>
       </c>
       <c r="R13" t="n">
-        <v>7026516</v>
+        <v>7026584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2070,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,7 +2080,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,7 +2232,7 @@
         <v>122979598</v>
       </c>
       <c r="B15" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010709</v>
+        <v>122980835</v>
       </c>
       <c r="B16" t="n">
-        <v>90951</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,34 +2386,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471477</v>
+        <v>471462</v>
       </c>
       <c r="R16" t="n">
-        <v>7026477</v>
+        <v>7026487</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,19 +2451,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,26 +2469,56 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010700</v>
+        <v>123010705</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,21 +2531,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2518,10 +2555,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471596</v>
+        <v>471553</v>
       </c>
       <c r="R17" t="n">
-        <v>7026584</v>
+        <v>7026553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2553,7 +2590,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2563,7 +2600,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2627,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010706</v>
+        <v>123010707</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2630,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471547</v>
+        <v>471506</v>
       </c>
       <c r="R18" t="n">
-        <v>7026555</v>
+        <v>7026544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2675,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122982580</v>
+        <v>123010709</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>90953</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2718,49 +2755,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471453</v>
+        <v>471477</v>
       </c>
       <c r="R19" t="n">
-        <v>7026499</v>
+        <v>7026477</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2787,14 +2812,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,56 +2835,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010707</v>
+        <v>123010711</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471506</v>
+        <v>471445</v>
       </c>
       <c r="R20" t="n">
-        <v>7026544</v>
+        <v>7026715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982584</v>
+        <v>122983059</v>
       </c>
       <c r="B3" t="n">
-        <v>90953</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471572</v>
+        <v>471480</v>
       </c>
       <c r="R3" t="n">
-        <v>7026541</v>
+        <v>7026453</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,6 +860,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122983059</v>
+        <v>122982584</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>90953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471480</v>
+        <v>471572</v>
       </c>
       <c r="R4" t="n">
-        <v>7026453</v>
+        <v>7026541</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,11 +992,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,31 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982234</v>
+        <v>122979397</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471541</v>
+        <v>471433</v>
       </c>
       <c r="R2" t="n">
-        <v>7026540</v>
+        <v>7026636</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +766,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122983059</v>
+        <v>122982234</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +823,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471480</v>
+        <v>471541</v>
       </c>
       <c r="R3" t="n">
-        <v>7026453</v>
+        <v>7026540</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +885,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982584</v>
+        <v>122982459</v>
       </c>
       <c r="B4" t="n">
-        <v>90953</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R4" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122982654</v>
+        <v>122982584</v>
       </c>
       <c r="B5" t="n">
-        <v>57431</v>
+        <v>90959</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471555</v>
+        <v>471572</v>
       </c>
       <c r="R5" t="n">
-        <v>7026552</v>
+        <v>7026541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982459</v>
+        <v>122982654</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1125,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471541</v>
+        <v>471555</v>
       </c>
       <c r="R6" t="n">
-        <v>7026540</v>
+        <v>7026552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122979397</v>
+        <v>122983059</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,34 +1240,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471433</v>
+        <v>471480</v>
       </c>
       <c r="R7" t="n">
-        <v>7026636</v>
+        <v>7026453</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010706</v>
+        <v>123010705</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471547</v>
+        <v>471553</v>
       </c>
       <c r="R8" t="n">
-        <v>7026555</v>
+        <v>7026553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122979829</v>
+        <v>122979598</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1489,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,13 +1527,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471465</v>
+        <v>471408</v>
       </c>
       <c r="R9" t="n">
-        <v>7026527</v>
+        <v>7026599</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,11 +1565,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,12 +1576,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1599,12 +1591,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1622,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010708</v>
+        <v>122979829</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,34 +1630,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471490</v>
+        <v>471465</v>
       </c>
       <c r="R10" t="n">
-        <v>7026516</v>
+        <v>7026527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,19 +1699,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:52</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,26 +1717,56 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010710</v>
+        <v>123010709</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>90959</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1779,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1774,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471465</v>
+        <v>471477</v>
       </c>
       <c r="R11" t="n">
-        <v>7026544</v>
+        <v>7026477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122982580</v>
+        <v>122980835</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1884,27 +1913,23 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471453</v>
+        <v>471462</v>
       </c>
       <c r="R12" t="n">
-        <v>7026499</v>
+        <v>7026487</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,7 +1963,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,12 +1997,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1995,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123010700</v>
+        <v>122982580</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,37 +2036,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471596</v>
+        <v>471453</v>
       </c>
       <c r="R13" t="n">
-        <v>7026584</v>
+        <v>7026499</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,19 +2105,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:09</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:09</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,26 +2123,56 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010703</v>
+        <v>123010710</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,39 +2185,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471553</v>
+        <v>471465</v>
       </c>
       <c r="R14" t="n">
-        <v>7026553</v>
+        <v>7026544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,7 +2244,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2197,12 +2254,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122979598</v>
+        <v>123010700</v>
       </c>
       <c r="B15" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,51 +2297,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471408</v>
+        <v>471596</v>
       </c>
       <c r="R15" t="n">
-        <v>7026599</v>
+        <v>7026584</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2316,11 +2354,21 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2329,51 +2377,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122980835</v>
+        <v>123010706</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2386,42 +2409,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471462</v>
+        <v>471547</v>
       </c>
       <c r="R16" t="n">
-        <v>7026487</v>
+        <v>7026555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2451,14 +2466,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,56 +2489,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010705</v>
+        <v>123010708</v>
       </c>
       <c r="B17" t="n">
-        <v>90957</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,21 +2521,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2555,10 +2545,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471553</v>
+        <v>471490</v>
       </c>
       <c r="R17" t="n">
-        <v>7026553</v>
+        <v>7026516</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2580,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2600,7 +2590,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2630,7 +2620,7 @@
         <v>123010707</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2739,10 +2729,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010709</v>
+        <v>123010711</v>
       </c>
       <c r="B19" t="n">
-        <v>90953</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,21 +2745,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2779,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471477</v>
+        <v>471445</v>
       </c>
       <c r="R19" t="n">
-        <v>7026477</v>
+        <v>7026715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,7 +2804,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2824,7 +2814,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010711</v>
+        <v>123010703</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,34 +2857,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471445</v>
+        <v>471553</v>
       </c>
       <c r="R20" t="n">
-        <v>7026715</v>
+        <v>7026553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2921,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2931,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122979397</v>
+        <v>122983059</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471433</v>
+        <v>471480</v>
       </c>
       <c r="R2" t="n">
-        <v>7026636</v>
+        <v>7026453</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,27 +774,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982234</v>
+        <v>122982584</v>
       </c>
       <c r="B3" t="n">
-        <v>90981</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +828,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471541</v>
+        <v>471572</v>
       </c>
       <c r="R3" t="n">
-        <v>7026540</v>
+        <v>7026541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982459</v>
+        <v>122982654</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +926,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471541</v>
+        <v>471555</v>
       </c>
       <c r="R4" t="n">
-        <v>7026540</v>
+        <v>7026552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122982584</v>
+        <v>122979397</v>
       </c>
       <c r="B5" t="n">
-        <v>90959</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471572</v>
+        <v>471433</v>
       </c>
       <c r="R5" t="n">
-        <v>7026541</v>
+        <v>7026636</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1103,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1097,6 +1116,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982654</v>
+        <v>122982234</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>90984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,47 +1169,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471555</v>
+        <v>471541</v>
       </c>
       <c r="R6" t="n">
-        <v>7026552</v>
+        <v>7026540</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122983059</v>
+        <v>122982459</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,42 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471480</v>
+        <v>471541</v>
       </c>
       <c r="R7" t="n">
-        <v>7026453</v>
+        <v>7026540</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,11 +1337,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1320,31 +1345,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010705</v>
+        <v>123010709</v>
       </c>
       <c r="B8" t="n">
-        <v>90963</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471553</v>
+        <v>471477</v>
       </c>
       <c r="R8" t="n">
-        <v>7026553</v>
+        <v>7026477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122979598</v>
+        <v>123010703</v>
       </c>
       <c r="B9" t="n">
-        <v>90981</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,51 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471408</v>
+        <v>471553</v>
       </c>
       <c r="R9" t="n">
-        <v>7026599</v>
+        <v>7026553</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,11 +1551,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1573,41 +1579,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1763,10 +1744,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010709</v>
+        <v>122980835</v>
       </c>
       <c r="B11" t="n">
-        <v>90959</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,34 +1760,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471477</v>
+        <v>471462</v>
       </c>
       <c r="R11" t="n">
-        <v>7026477</v>
+        <v>7026487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,19 +1825,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,26 +1843,56 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122980835</v>
+        <v>123010710</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,42 +1905,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471462</v>
+        <v>471465</v>
       </c>
       <c r="R12" t="n">
-        <v>7026487</v>
+        <v>7026544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1956,14 +1962,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,56 +1985,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122982580</v>
+        <v>122979598</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,34 +2017,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2072,13 +2055,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471453</v>
+        <v>471408</v>
       </c>
       <c r="R13" t="n">
-        <v>7026499</v>
+        <v>7026599</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2110,11 +2093,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2126,12 +2104,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2146,12 +2119,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2169,10 +2142,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010710</v>
+        <v>123010707</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2209,7 +2182,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471465</v>
+        <v>471506</v>
       </c>
       <c r="R14" t="n">
         <v>7026544</v>
@@ -2244,7 +2217,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2254,7 +2227,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2284,7 +2257,7 @@
         <v>123010700</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2393,10 +2366,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010706</v>
+        <v>123010705</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>90966</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2409,21 +2382,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2433,10 +2406,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471547</v>
+        <v>471553</v>
       </c>
       <c r="R16" t="n">
-        <v>7026555</v>
+        <v>7026553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2508,7 +2481,7 @@
         <v>123010708</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2617,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010707</v>
+        <v>122982580</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2633,37 +2606,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471506</v>
+        <v>471453</v>
       </c>
       <c r="R18" t="n">
-        <v>7026544</v>
+        <v>7026499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,19 +2675,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:58</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,26 +2693,56 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010711</v>
+        <v>123010706</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2769,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471445</v>
+        <v>471547</v>
       </c>
       <c r="R19" t="n">
-        <v>7026715</v>
+        <v>7026555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2804,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2814,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2841,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010703</v>
+        <v>123010711</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2857,39 +2867,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471553</v>
+        <v>471445</v>
       </c>
       <c r="R20" t="n">
-        <v>7026553</v>
+        <v>7026715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2931,12 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122982584</v>
+        <v>122983059</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471572</v>
+        <v>471480</v>
       </c>
       <c r="R2" t="n">
-        <v>7026541</v>
+        <v>7026453</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +758,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122983059</v>
+        <v>122982584</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471480</v>
+        <v>471572</v>
       </c>
       <c r="R3" t="n">
-        <v>7026453</v>
+        <v>7026541</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +890,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122983059</v>
+        <v>122982459</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471480</v>
+        <v>471541</v>
       </c>
       <c r="R2" t="n">
-        <v>7026453</v>
+        <v>7026540</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +753,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122982584</v>
+        <v>122982234</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>91001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471572</v>
+        <v>471541</v>
       </c>
       <c r="R3" t="n">
-        <v>7026541</v>
+        <v>7026540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122982654</v>
+        <v>122983059</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,14 +912,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471555</v>
+        <v>471480</v>
       </c>
       <c r="R4" t="n">
-        <v>7026552</v>
+        <v>7026453</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,6 +962,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1009,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979397</v>
+        <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>57437</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,41 +1028,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471433</v>
+        <v>471555</v>
       </c>
       <c r="R5" t="n">
-        <v>7026636</v>
+        <v>7026552</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,11 +1103,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1116,31 +1111,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1157,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122982234</v>
+        <v>122979397</v>
       </c>
       <c r="B6" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471541</v>
+        <v>471433</v>
       </c>
       <c r="R6" t="n">
-        <v>7026540</v>
+        <v>7026636</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,6 +1205,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1243,6 +1218,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122982459</v>
+        <v>122982584</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471541</v>
+        <v>471572</v>
       </c>
       <c r="R7" t="n">
-        <v>7026540</v>
+        <v>7026541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123010709</v>
+        <v>123010710</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471477</v>
+        <v>471465</v>
       </c>
       <c r="R8" t="n">
-        <v>7026477</v>
+        <v>7026544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010703</v>
+        <v>123010709</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>90979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471553</v>
+        <v>471477</v>
       </c>
       <c r="R9" t="n">
-        <v>7026553</v>
+        <v>7026477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Både gamla och färska ringhack.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122979829</v>
+        <v>122980835</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,21 +1626,17 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471465</v>
+        <v>471462</v>
       </c>
       <c r="R10" t="n">
-        <v>7026527</v>
+        <v>7026487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1673,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1692,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1721,12 +1707,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1744,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122980835</v>
+        <v>122979829</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,17 +1771,21 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471462</v>
+        <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026487</v>
+        <v>7026527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1822,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1841,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1866,12 +1856,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1889,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010710</v>
+        <v>123010703</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,34 +1895,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471465</v>
+        <v>471553</v>
       </c>
       <c r="R12" t="n">
-        <v>7026544</v>
+        <v>7026553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1969,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Både gamla och färska ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122979598</v>
+        <v>122982580</v>
       </c>
       <c r="B13" t="n">
-        <v>90984</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,36 +2017,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2055,13 +2053,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471408</v>
+        <v>471453</v>
       </c>
       <c r="R13" t="n">
-        <v>7026599</v>
+        <v>7026499</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2093,6 +2091,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2104,7 +2107,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2119,12 +2127,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2145,7 +2153,7 @@
         <v>123010707</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2254,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010700</v>
+        <v>123010711</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,10 +2302,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471596</v>
+        <v>471445</v>
       </c>
       <c r="R15" t="n">
-        <v>7026584</v>
+        <v>7026715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2337,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,7 +2347,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,10 +2374,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123010705</v>
+        <v>122979598</v>
       </c>
       <c r="B16" t="n">
-        <v>90966</v>
+        <v>91001</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,37 +2390,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471553</v>
+        <v>471408</v>
       </c>
       <c r="R16" t="n">
-        <v>7026553</v>
+        <v>7026599</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,21 +2461,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2462,26 +2474,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123010708</v>
+        <v>123010706</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2518,10 +2555,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471490</v>
+        <v>471547</v>
       </c>
       <c r="R17" t="n">
-        <v>7026516</v>
+        <v>7026555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2553,7 +2590,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2563,7 +2600,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2627,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122982580</v>
+        <v>123010700</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,49 +2643,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471453</v>
+        <v>471596</v>
       </c>
       <c r="R18" t="n">
-        <v>7026499</v>
+        <v>7026584</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2675,14 +2700,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och även en del äldre ringhack längs flera meter på en granstam. Fyndplatsen finns i äldre granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,56 +2723,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010706</v>
+        <v>123010708</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471547</v>
+        <v>471490</v>
       </c>
       <c r="R19" t="n">
-        <v>7026555</v>
+        <v>7026516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010711</v>
+        <v>123010705</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471445</v>
+        <v>471553</v>
       </c>
       <c r="R20" t="n">
-        <v>7026715</v>
+        <v>7026553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -2739,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010708</v>
+        <v>123010705</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471490</v>
+        <v>471553</v>
       </c>
       <c r="R19" t="n">
-        <v>7026516</v>
+        <v>7026553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010705</v>
+        <v>123010708</v>
       </c>
       <c r="B20" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471553</v>
+        <v>471490</v>
       </c>
       <c r="R20" t="n">
-        <v>7026553</v>
+        <v>7026516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010709</v>
+        <v>122980835</v>
       </c>
       <c r="B9" t="n">
-        <v>90979</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471477</v>
+        <v>471462</v>
       </c>
       <c r="R9" t="n">
-        <v>7026477</v>
+        <v>7026487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,19 +1554,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,23 +1572,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122980835</v>
+        <v>122979829</v>
       </c>
       <c r="B10" t="n">
         <v>57487</v>
@@ -1626,17 +1659,21 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471462</v>
+        <v>471465</v>
       </c>
       <c r="R10" t="n">
-        <v>7026487</v>
+        <v>7026527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1729,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1707,12 +1744,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1730,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122979829</v>
+        <v>123010709</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>90979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,46 +1783,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471465</v>
+        <v>471477</v>
       </c>
       <c r="R11" t="n">
-        <v>7026527</v>
+        <v>7026477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,14 +1840,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,46 +1863,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123010705</v>
+        <v>123010708</v>
       </c>
       <c r="B19" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471553</v>
+        <v>471490</v>
       </c>
       <c r="R19" t="n">
-        <v>7026553</v>
+        <v>7026516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123010708</v>
+        <v>123010705</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471490</v>
+        <v>471553</v>
       </c>
       <c r="R20" t="n">
-        <v>7026516</v>
+        <v>7026553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122980835</v>
+        <v>123010709</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>90979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,42 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyrsved, Långmyrsved, Jmt</t>
+          <t>Aspås V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471462</v>
+        <v>471477</v>
       </c>
       <c r="R9" t="n">
-        <v>7026487</v>
+        <v>7026477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,14 +1546,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,53 +1569,23 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122979829</v>
+        <v>122980835</v>
       </c>
       <c r="B10" t="n">
         <v>57487</v>
@@ -1659,21 +1626,17 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471465</v>
+        <v>471462</v>
       </c>
       <c r="R10" t="n">
-        <v>7026527</v>
+        <v>7026487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1673,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på en stående död granstam som delvis är avbarkad. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1692,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1744,12 +1707,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1767,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010709</v>
+        <v>122979829</v>
       </c>
       <c r="B11" t="n">
-        <v>90979</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,34 +1746,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspås V, Jmt</t>
+          <t>Långmyrsved, Långmyrsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471477</v>
+        <v>471465</v>
       </c>
       <c r="R11" t="n">
-        <v>7026477</v>
+        <v>7026527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,19 +1815,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:46</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,16 +1833,46 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1019,11 +1019,11 @@
         <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>57437</v>
+        <v>57441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1019,12 +1019,7 @@
         <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46118-2024 artfynd.xlsx
+++ b/artfynd/A 46118-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>122982654</v>
       </c>
       <c r="B5" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
